--- a/files/power_outage_area/Power_Cuts_2026_Area_Summary.xlsx
+++ b/files/power_outage_area/Power_Cuts_2026_Area_Summary.xlsx
@@ -643,22 +643,22 @@
         </is>
       </c>
       <c r="C2" s="9" t="n">
-        <v>38444</v>
+        <v>96529</v>
       </c>
       <c r="D2" s="9" t="n">
-        <v>47.07985843222259</v>
+        <v>44.40095122882389</v>
       </c>
       <c r="E2" s="9" t="inlineStr"/>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>70840:00:00</t>
+          <t>180652:00:00</t>
         </is>
       </c>
       <c r="G2" s="9" t="n">
-        <v>70840</v>
+        <v>180652</v>
       </c>
       <c r="H2" s="9" t="n">
-        <v>47.05257214971273</v>
+        <v>44.79267654665057</v>
       </c>
     </row>
     <row r="3">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>17719</v>
+        <v>55483</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>21.69930318282572</v>
+        <v>25.52080698058444</v>
       </c>
       <c r="E3" s="10" t="inlineStr"/>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>30854:00:00</t>
+          <t>103907:00:00</t>
         </is>
       </c>
       <c r="G3" s="10" t="n">
-        <v>30854</v>
+        <v>103907</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>20.49350735611571</v>
+        <v>25.7637482116601</v>
       </c>
     </row>
     <row r="4">
@@ -703,22 +703,22 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>25494</v>
+        <v>65391</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>31.22083838495169</v>
+        <v>30.07824179059167</v>
       </c>
       <c r="E4" s="11" t="inlineStr"/>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>48861:00:00</t>
+          <t>118748:00:00</t>
         </is>
       </c>
       <c r="G4" s="11" t="n">
-        <v>48861</v>
+        <v>118748</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>32.45392049417157</v>
+        <v>29.44357524168933</v>
       </c>
     </row>
   </sheetData>
@@ -1106,73 +1106,73 @@
         <v>4073</v>
       </c>
       <c r="P2" s="9" t="n">
-        <v>0</v>
+        <v>2670</v>
       </c>
       <c r="Q2" s="9" t="n">
-        <v>0</v>
+        <v>2687</v>
       </c>
       <c r="R2" s="9" t="n">
-        <v>0</v>
+        <v>2262</v>
       </c>
       <c r="S2" s="9" t="n">
-        <v>0</v>
+        <v>2698</v>
       </c>
       <c r="T2" s="9" t="n">
-        <v>0</v>
+        <v>2876</v>
       </c>
       <c r="U2" s="9" t="n">
-        <v>0</v>
+        <v>3048</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>0</v>
+        <v>2858</v>
       </c>
       <c r="W2" s="9" t="n">
-        <v>0</v>
+        <v>1610</v>
       </c>
       <c r="X2" s="9" t="n">
-        <v>0</v>
+        <v>2195</v>
       </c>
       <c r="Y2" s="9" t="n">
-        <v>0</v>
+        <v>2612</v>
       </c>
       <c r="Z2" s="9" t="n">
-        <v>0</v>
+        <v>2880</v>
       </c>
       <c r="AA2" s="9" t="n">
-        <v>0</v>
+        <v>2451</v>
       </c>
       <c r="AB2" s="9" t="n">
-        <v>0</v>
+        <v>2677</v>
       </c>
       <c r="AC2" s="9" t="n">
-        <v>0</v>
+        <v>2387</v>
       </c>
       <c r="AD2" s="9" t="n">
-        <v>0</v>
+        <v>2417</v>
       </c>
       <c r="AE2" s="9" t="n">
-        <v>0</v>
+        <v>2901</v>
       </c>
       <c r="AF2" s="9" t="n">
-        <v>0</v>
+        <v>2852</v>
       </c>
       <c r="AG2" s="9" t="n">
-        <v>0</v>
+        <v>2465</v>
       </c>
       <c r="AH2" s="9" t="n">
-        <v>0</v>
+        <v>2487</v>
       </c>
       <c r="AI2" s="9" t="n">
-        <v>0</v>
+        <v>2079</v>
       </c>
       <c r="AJ2" s="9" t="n">
-        <v>0</v>
+        <v>2615</v>
       </c>
       <c r="AK2" s="9" t="n">
-        <v>0</v>
+        <v>2167</v>
       </c>
       <c r="AL2" s="9" t="n">
-        <v>0</v>
+        <v>2191</v>
       </c>
       <c r="AM2" s="9" t="n">
         <v>0</v>
@@ -1269,73 +1269,73 @@
         <v>1823</v>
       </c>
       <c r="P3" s="10" t="n">
-        <v>0</v>
+        <v>1439</v>
       </c>
       <c r="Q3" s="10" t="n">
-        <v>0</v>
+        <v>1417</v>
       </c>
       <c r="R3" s="10" t="n">
-        <v>0</v>
+        <v>1068</v>
       </c>
       <c r="S3" s="10" t="n">
-        <v>0</v>
+        <v>1460</v>
       </c>
       <c r="T3" s="10" t="n">
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="U3" s="10" t="n">
-        <v>0</v>
+        <v>2140</v>
       </c>
       <c r="V3" s="10" t="n">
-        <v>0</v>
+        <v>1959</v>
       </c>
       <c r="W3" s="10" t="n">
-        <v>0</v>
+        <v>1087</v>
       </c>
       <c r="X3" s="10" t="n">
-        <v>0</v>
+        <v>1654</v>
       </c>
       <c r="Y3" s="10" t="n">
-        <v>0</v>
+        <v>1684</v>
       </c>
       <c r="Z3" s="10" t="n">
-        <v>0</v>
+        <v>1593</v>
       </c>
       <c r="AA3" s="10" t="n">
-        <v>0</v>
+        <v>1452</v>
       </c>
       <c r="AB3" s="10" t="n">
-        <v>0</v>
+        <v>1713</v>
       </c>
       <c r="AC3" s="10" t="n">
-        <v>0</v>
+        <v>1611</v>
       </c>
       <c r="AD3" s="10" t="n">
-        <v>0</v>
+        <v>1721</v>
       </c>
       <c r="AE3" s="10" t="n">
-        <v>0</v>
+        <v>2343</v>
       </c>
       <c r="AF3" s="10" t="n">
-        <v>0</v>
+        <v>1805</v>
       </c>
       <c r="AG3" s="10" t="n">
-        <v>0</v>
+        <v>2167</v>
       </c>
       <c r="AH3" s="10" t="n">
-        <v>0</v>
+        <v>1954</v>
       </c>
       <c r="AI3" s="10" t="n">
-        <v>0</v>
+        <v>1659</v>
       </c>
       <c r="AJ3" s="10" t="n">
-        <v>0</v>
+        <v>1686</v>
       </c>
       <c r="AK3" s="10" t="n">
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AL3" s="10" t="n">
-        <v>0</v>
+        <v>1488</v>
       </c>
       <c r="AM3" s="10" t="n">
         <v>0</v>
@@ -1432,73 +1432,73 @@
         <v>3244</v>
       </c>
       <c r="P4" s="11" t="n">
-        <v>0</v>
+        <v>1924</v>
       </c>
       <c r="Q4" s="11" t="n">
-        <v>0</v>
+        <v>1661</v>
       </c>
       <c r="R4" s="11" t="n">
-        <v>0</v>
+        <v>1646</v>
       </c>
       <c r="S4" s="11" t="n">
-        <v>0</v>
+        <v>1858</v>
       </c>
       <c r="T4" s="11" t="n">
-        <v>0</v>
+        <v>1578</v>
       </c>
       <c r="U4" s="11" t="n">
-        <v>0</v>
+        <v>1937</v>
       </c>
       <c r="V4" s="11" t="n">
-        <v>0</v>
+        <v>2356</v>
       </c>
       <c r="W4" s="11" t="n">
-        <v>0</v>
+        <v>1727</v>
       </c>
       <c r="X4" s="11" t="n">
-        <v>0</v>
+        <v>2115</v>
       </c>
       <c r="Y4" s="11" t="n">
-        <v>0</v>
+        <v>1893</v>
       </c>
       <c r="Z4" s="11" t="n">
-        <v>0</v>
+        <v>1674</v>
       </c>
       <c r="AA4" s="11" t="n">
-        <v>0</v>
+        <v>1381</v>
       </c>
       <c r="AB4" s="11" t="n">
-        <v>0</v>
+        <v>1536</v>
       </c>
       <c r="AC4" s="11" t="n">
-        <v>0</v>
+        <v>1761</v>
       </c>
       <c r="AD4" s="11" t="n">
-        <v>0</v>
+        <v>1546</v>
       </c>
       <c r="AE4" s="11" t="n">
-        <v>0</v>
+        <v>2138</v>
       </c>
       <c r="AF4" s="11" t="n">
-        <v>0</v>
+        <v>1609</v>
       </c>
       <c r="AG4" s="11" t="n">
-        <v>0</v>
+        <v>1874</v>
       </c>
       <c r="AH4" s="11" t="n">
-        <v>0</v>
+        <v>1781</v>
       </c>
       <c r="AI4" s="11" t="n">
-        <v>0</v>
+        <v>1633</v>
       </c>
       <c r="AJ4" s="11" t="n">
-        <v>0</v>
+        <v>1494</v>
       </c>
       <c r="AK4" s="11" t="n">
-        <v>0</v>
+        <v>1334</v>
       </c>
       <c r="AL4" s="11" t="n">
-        <v>0</v>
+        <v>1441</v>
       </c>
       <c r="AM4" s="11" t="n">
         <v>0</v>
@@ -1595,73 +1595,73 @@
         <v>9140</v>
       </c>
       <c r="P5" s="12" t="n">
-        <v>0</v>
+        <v>6033</v>
       </c>
       <c r="Q5" s="12" t="n">
-        <v>0</v>
+        <v>5765</v>
       </c>
       <c r="R5" s="12" t="n">
-        <v>0</v>
+        <v>4976</v>
       </c>
       <c r="S5" s="12" t="n">
-        <v>0</v>
+        <v>6016</v>
       </c>
       <c r="T5" s="12" t="n">
-        <v>0</v>
+        <v>5734</v>
       </c>
       <c r="U5" s="12" t="n">
-        <v>0</v>
+        <v>7125</v>
       </c>
       <c r="V5" s="12" t="n">
-        <v>0</v>
+        <v>7173</v>
       </c>
       <c r="W5" s="12" t="n">
-        <v>0</v>
+        <v>4424</v>
       </c>
       <c r="X5" s="12" t="n">
-        <v>0</v>
+        <v>5964</v>
       </c>
       <c r="Y5" s="12" t="n">
-        <v>0</v>
+        <v>6189</v>
       </c>
       <c r="Z5" s="12" t="n">
-        <v>0</v>
+        <v>6147</v>
       </c>
       <c r="AA5" s="12" t="n">
-        <v>0</v>
+        <v>5284</v>
       </c>
       <c r="AB5" s="12" t="n">
-        <v>0</v>
+        <v>5926</v>
       </c>
       <c r="AC5" s="12" t="n">
-        <v>0</v>
+        <v>5759</v>
       </c>
       <c r="AD5" s="12" t="n">
-        <v>0</v>
+        <v>5684</v>
       </c>
       <c r="AE5" s="12" t="n">
-        <v>0</v>
+        <v>7382</v>
       </c>
       <c r="AF5" s="12" t="n">
-        <v>0</v>
+        <v>6266</v>
       </c>
       <c r="AG5" s="12" t="n">
-        <v>0</v>
+        <v>6506</v>
       </c>
       <c r="AH5" s="12" t="n">
-        <v>0</v>
+        <v>6222</v>
       </c>
       <c r="AI5" s="12" t="n">
-        <v>0</v>
+        <v>5371</v>
       </c>
       <c r="AJ5" s="12" t="n">
-        <v>0</v>
+        <v>5795</v>
       </c>
       <c r="AK5" s="12" t="n">
-        <v>0</v>
+        <v>4885</v>
       </c>
       <c r="AL5" s="12" t="n">
-        <v>0</v>
+        <v>5120</v>
       </c>
       <c r="AM5" s="12" t="n">
         <v>0</v>
@@ -2094,73 +2094,73 @@
         <v>9294</v>
       </c>
       <c r="P2" s="9" t="n">
-        <v>0</v>
+        <v>5630</v>
       </c>
       <c r="Q2" s="9" t="n">
-        <v>0</v>
+        <v>5485</v>
       </c>
       <c r="R2" s="9" t="n">
-        <v>0</v>
+        <v>5167</v>
       </c>
       <c r="S2" s="9" t="n">
-        <v>0</v>
+        <v>5660</v>
       </c>
       <c r="T2" s="9" t="n">
-        <v>0</v>
+        <v>5818</v>
       </c>
       <c r="U2" s="9" t="n">
-        <v>0</v>
+        <v>5621</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>0</v>
+        <v>5405</v>
       </c>
       <c r="W2" s="9" t="n">
-        <v>0</v>
+        <v>2868</v>
       </c>
       <c r="X2" s="9" t="n">
-        <v>0</v>
+        <v>3882</v>
       </c>
       <c r="Y2" s="9" t="n">
-        <v>0</v>
+        <v>5064</v>
       </c>
       <c r="Z2" s="9" t="n">
-        <v>0</v>
+        <v>6432</v>
       </c>
       <c r="AA2" s="9" t="n">
-        <v>0</v>
+        <v>4591</v>
       </c>
       <c r="AB2" s="9" t="n">
-        <v>0</v>
+        <v>4739</v>
       </c>
       <c r="AC2" s="9" t="n">
-        <v>0</v>
+        <v>4684</v>
       </c>
       <c r="AD2" s="9" t="n">
-        <v>0</v>
+        <v>4029</v>
       </c>
       <c r="AE2" s="9" t="n">
-        <v>0</v>
+        <v>5245</v>
       </c>
       <c r="AF2" s="9" t="n">
-        <v>0</v>
+        <v>4473</v>
       </c>
       <c r="AG2" s="9" t="n">
-        <v>0</v>
+        <v>4463</v>
       </c>
       <c r="AH2" s="9" t="n">
-        <v>0</v>
+        <v>4175</v>
       </c>
       <c r="AI2" s="9" t="n">
-        <v>0</v>
+        <v>3801</v>
       </c>
       <c r="AJ2" s="9" t="n">
-        <v>0</v>
+        <v>4745</v>
       </c>
       <c r="AK2" s="9" t="n">
-        <v>0</v>
+        <v>4143</v>
       </c>
       <c r="AL2" s="9" t="n">
-        <v>0</v>
+        <v>3692</v>
       </c>
       <c r="AM2" s="9" t="n">
         <v>0</v>
@@ -2257,73 +2257,73 @@
         <v>4598</v>
       </c>
       <c r="P3" s="10" t="n">
-        <v>0</v>
+        <v>3066</v>
       </c>
       <c r="Q3" s="10" t="n">
-        <v>0</v>
+        <v>2748</v>
       </c>
       <c r="R3" s="10" t="n">
-        <v>0</v>
+        <v>2188</v>
       </c>
       <c r="S3" s="10" t="n">
-        <v>0</v>
+        <v>3119</v>
       </c>
       <c r="T3" s="10" t="n">
-        <v>0</v>
+        <v>2108</v>
       </c>
       <c r="U3" s="10" t="n">
-        <v>0</v>
+        <v>3306</v>
       </c>
       <c r="V3" s="10" t="n">
-        <v>0</v>
+        <v>3085</v>
       </c>
       <c r="W3" s="10" t="n">
-        <v>0</v>
+        <v>1981</v>
       </c>
       <c r="X3" s="10" t="n">
-        <v>0</v>
+        <v>3272</v>
       </c>
       <c r="Y3" s="10" t="n">
-        <v>0</v>
+        <v>3214</v>
       </c>
       <c r="Z3" s="10" t="n">
-        <v>0</v>
+        <v>3418</v>
       </c>
       <c r="AA3" s="10" t="n">
-        <v>0</v>
+        <v>2942</v>
       </c>
       <c r="AB3" s="10" t="n">
-        <v>0</v>
+        <v>3589</v>
       </c>
       <c r="AC3" s="10" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="AD3" s="10" t="n">
-        <v>0</v>
+        <v>3425</v>
       </c>
       <c r="AE3" s="10" t="n">
-        <v>0</v>
+        <v>4756</v>
       </c>
       <c r="AF3" s="10" t="n">
-        <v>0</v>
+        <v>3297</v>
       </c>
       <c r="AG3" s="10" t="n">
-        <v>0</v>
+        <v>4209</v>
       </c>
       <c r="AH3" s="10" t="n">
-        <v>0</v>
+        <v>3295</v>
       </c>
       <c r="AI3" s="10" t="n">
-        <v>0</v>
+        <v>3153</v>
       </c>
       <c r="AJ3" s="10" t="n">
-        <v>0</v>
+        <v>3937</v>
       </c>
       <c r="AK3" s="10" t="n">
-        <v>0</v>
+        <v>2687</v>
       </c>
       <c r="AL3" s="10" t="n">
-        <v>0</v>
+        <v>2940</v>
       </c>
       <c r="AM3" s="10" t="n">
         <v>0</v>
@@ -2420,73 +2420,73 @@
         <v>7289</v>
       </c>
       <c r="P4" s="11" t="n">
-        <v>0</v>
+        <v>3101</v>
       </c>
       <c r="Q4" s="11" t="n">
-        <v>0</v>
+        <v>3133</v>
       </c>
       <c r="R4" s="11" t="n">
-        <v>0</v>
+        <v>2977</v>
       </c>
       <c r="S4" s="11" t="n">
-        <v>0</v>
+        <v>2944</v>
       </c>
       <c r="T4" s="11" t="n">
-        <v>0</v>
+        <v>2493</v>
       </c>
       <c r="U4" s="11" t="n">
-        <v>0</v>
+        <v>2691</v>
       </c>
       <c r="V4" s="11" t="n">
-        <v>0</v>
+        <v>3205</v>
       </c>
       <c r="W4" s="11" t="n">
-        <v>0</v>
+        <v>2306</v>
       </c>
       <c r="X4" s="11" t="n">
-        <v>0</v>
+        <v>3375</v>
       </c>
       <c r="Y4" s="11" t="n">
-        <v>0</v>
+        <v>3834</v>
       </c>
       <c r="Z4" s="11" t="n">
-        <v>0</v>
+        <v>2864</v>
       </c>
       <c r="AA4" s="11" t="n">
-        <v>0</v>
+        <v>2676</v>
       </c>
       <c r="AB4" s="11" t="n">
-        <v>0</v>
+        <v>2836</v>
       </c>
       <c r="AC4" s="11" t="n">
-        <v>0</v>
+        <v>3063</v>
       </c>
       <c r="AD4" s="11" t="n">
-        <v>0</v>
+        <v>2883</v>
       </c>
       <c r="AE4" s="11" t="n">
-        <v>0</v>
+        <v>3587</v>
       </c>
       <c r="AF4" s="11" t="n">
-        <v>0</v>
+        <v>2591</v>
       </c>
       <c r="AG4" s="11" t="n">
-        <v>0</v>
+        <v>3938</v>
       </c>
       <c r="AH4" s="11" t="n">
-        <v>0</v>
+        <v>3453</v>
       </c>
       <c r="AI4" s="11" t="n">
-        <v>0</v>
+        <v>3238</v>
       </c>
       <c r="AJ4" s="11" t="n">
-        <v>0</v>
+        <v>2887</v>
       </c>
       <c r="AK4" s="11" t="n">
-        <v>0</v>
+        <v>2826</v>
       </c>
       <c r="AL4" s="11" t="n">
-        <v>0</v>
+        <v>2986</v>
       </c>
       <c r="AM4" s="11" t="n">
         <v>0</v>
@@ -2583,73 +2583,73 @@
         <v>21181</v>
       </c>
       <c r="P5" s="12" t="n">
-        <v>0</v>
+        <v>11797</v>
       </c>
       <c r="Q5" s="12" t="n">
-        <v>0</v>
+        <v>11366</v>
       </c>
       <c r="R5" s="12" t="n">
-        <v>0</v>
+        <v>10332</v>
       </c>
       <c r="S5" s="12" t="n">
-        <v>0</v>
+        <v>11723</v>
       </c>
       <c r="T5" s="12" t="n">
-        <v>0</v>
+        <v>10419</v>
       </c>
       <c r="U5" s="12" t="n">
-        <v>0</v>
+        <v>11618</v>
       </c>
       <c r="V5" s="12" t="n">
-        <v>0</v>
+        <v>11695</v>
       </c>
       <c r="W5" s="12" t="n">
-        <v>0</v>
+        <v>7155</v>
       </c>
       <c r="X5" s="12" t="n">
-        <v>0</v>
+        <v>10529</v>
       </c>
       <c r="Y5" s="12" t="n">
-        <v>0</v>
+        <v>12112</v>
       </c>
       <c r="Z5" s="12" t="n">
-        <v>0</v>
+        <v>12714</v>
       </c>
       <c r="AA5" s="12" t="n">
-        <v>0</v>
+        <v>10209</v>
       </c>
       <c r="AB5" s="12" t="n">
-        <v>0</v>
+        <v>11164</v>
       </c>
       <c r="AC5" s="12" t="n">
-        <v>0</v>
+        <v>11065</v>
       </c>
       <c r="AD5" s="12" t="n">
-        <v>0</v>
+        <v>10337</v>
       </c>
       <c r="AE5" s="12" t="n">
-        <v>0</v>
+        <v>13588</v>
       </c>
       <c r="AF5" s="12" t="n">
-        <v>0</v>
+        <v>10361</v>
       </c>
       <c r="AG5" s="12" t="n">
-        <v>0</v>
+        <v>12610</v>
       </c>
       <c r="AH5" s="12" t="n">
-        <v>0</v>
+        <v>10923</v>
       </c>
       <c r="AI5" s="12" t="n">
-        <v>0</v>
+        <v>10192</v>
       </c>
       <c r="AJ5" s="12" t="n">
-        <v>0</v>
+        <v>11569</v>
       </c>
       <c r="AK5" s="12" t="n">
-        <v>0</v>
+        <v>9656</v>
       </c>
       <c r="AL5" s="12" t="n">
-        <v>0</v>
+        <v>9618</v>
       </c>
       <c r="AM5" s="12" t="n">
         <v>0</v>
@@ -3018,16 +3018,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2670</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1439</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1924</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>6033</v>
       </c>
     </row>
     <row r="17">
@@ -3037,16 +3037,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>2687</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1417</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1661</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>5765</v>
       </c>
     </row>
     <row r="18">
@@ -3056,16 +3056,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>2262</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1068</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1646</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>4976</v>
       </c>
     </row>
     <row r="19">
@@ -3075,16 +3075,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>2698</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1460</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1858</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>6016</v>
       </c>
     </row>
     <row r="20">
@@ -3094,16 +3094,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>2876</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1578</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>5734</v>
       </c>
     </row>
     <row r="21">
@@ -3113,16 +3113,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>3048</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>2140</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1937</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>7125</v>
       </c>
     </row>
     <row r="22">
@@ -3132,16 +3132,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>2858</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1959</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>2356</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>7173</v>
       </c>
     </row>
     <row r="23">
@@ -3151,16 +3151,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1610</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1087</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1727</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>4424</v>
       </c>
     </row>
     <row r="24">
@@ -3170,16 +3170,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>2195</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1654</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2115</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>5964</v>
       </c>
     </row>
     <row r="25">
@@ -3189,16 +3189,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>2612</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1684</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1893</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>6189</v>
       </c>
     </row>
     <row r="26">
@@ -3208,16 +3208,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>2880</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1593</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1674</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>6147</v>
       </c>
     </row>
     <row r="27">
@@ -3227,16 +3227,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>2451</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1452</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1381</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>5284</v>
       </c>
     </row>
     <row r="28">
@@ -3246,16 +3246,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>2677</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1713</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1536</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>5926</v>
       </c>
     </row>
     <row r="29">
@@ -3265,16 +3265,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>2387</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1611</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1761</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>5759</v>
       </c>
     </row>
     <row r="30">
@@ -3284,16 +3284,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>2417</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1721</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1546</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>5684</v>
       </c>
     </row>
     <row r="31">
@@ -3303,16 +3303,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>2901</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>2343</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>2138</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>7382</v>
       </c>
     </row>
     <row r="32">
@@ -3322,16 +3322,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>2852</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1805</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1609</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>6266</v>
       </c>
     </row>
     <row r="33">
@@ -3341,16 +3341,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>2465</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>2167</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1874</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>6506</v>
       </c>
     </row>
     <row r="34">
@@ -3360,16 +3360,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>2487</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1954</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1781</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>6222</v>
       </c>
     </row>
     <row r="35">
@@ -3379,16 +3379,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>2079</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>1659</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1633</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>5371</v>
       </c>
     </row>
     <row r="36">
@@ -3398,16 +3398,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>2615</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>1686</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>1494</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>5795</v>
       </c>
     </row>
     <row r="37">
@@ -3417,16 +3417,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>2167</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1334</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>4885</v>
       </c>
     </row>
     <row r="38">
@@ -3436,16 +3436,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>2191</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1488</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1441</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="39">
@@ -4054,16 +4054,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>5630</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3066</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>3101</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>11797</v>
       </c>
     </row>
     <row r="17">
@@ -4073,16 +4073,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>5485</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>2748</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>3133</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>11366</v>
       </c>
     </row>
     <row r="18">
@@ -4092,16 +4092,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>5167</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2188</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2977</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>10332</v>
       </c>
     </row>
     <row r="19">
@@ -4111,16 +4111,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>5660</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3119</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2944</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>11723</v>
       </c>
     </row>
     <row r="20">
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>5818</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2108</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>2493</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>10419</v>
       </c>
     </row>
     <row r="21">
@@ -4149,16 +4149,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>5621</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>3306</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2691</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>11618</v>
       </c>
     </row>
     <row r="22">
@@ -4168,16 +4168,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>5405</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>3085</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>3205</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>11695</v>
       </c>
     </row>
     <row r="23">
@@ -4187,16 +4187,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>2868</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1981</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>2306</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>7155</v>
       </c>
     </row>
     <row r="24">
@@ -4206,16 +4206,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>3882</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>3272</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>3375</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>10529</v>
       </c>
     </row>
     <row r="25">
@@ -4225,16 +4225,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>5064</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>3214</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>3834</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>12112</v>
       </c>
     </row>
     <row r="26">
@@ -4244,16 +4244,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>6432</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>3418</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>2864</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>12714</v>
       </c>
     </row>
     <row r="27">
@@ -4263,16 +4263,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>4591</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>2942</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>2676</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>10209</v>
       </c>
     </row>
     <row r="28">
@@ -4282,16 +4282,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>4739</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>3589</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>2836</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>11164</v>
       </c>
     </row>
     <row r="29">
@@ -4301,16 +4301,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>4684</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>3063</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>11065</v>
       </c>
     </row>
     <row r="30">
@@ -4320,16 +4320,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>4029</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>3425</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>2883</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>10337</v>
       </c>
     </row>
     <row r="31">
@@ -4339,16 +4339,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>5245</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>4756</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>3587</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>13588</v>
       </c>
     </row>
     <row r="32">
@@ -4358,16 +4358,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>4473</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>3297</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>2591</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>10361</v>
       </c>
     </row>
     <row r="33">
@@ -4377,16 +4377,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>4463</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>4209</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>3938</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>12610</v>
       </c>
     </row>
     <row r="34">
@@ -4396,16 +4396,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>4175</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>3295</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>3453</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>10923</v>
       </c>
     </row>
     <row r="35">
@@ -4415,16 +4415,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>3801</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>3153</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>3238</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>10192</v>
       </c>
     </row>
     <row r="36">
@@ -4434,16 +4434,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>4745</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>3937</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>2887</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>11569</v>
       </c>
     </row>
     <row r="37">
@@ -4453,16 +4453,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>4143</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>2687</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>2826</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>9656</v>
       </c>
     </row>
     <row r="38">
@@ -4472,16 +4472,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>3692</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>2940</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>2986</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>9618</v>
       </c>
     </row>
     <row r="39">
@@ -5294,16 +5294,16 @@
         <v>5020</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>2670</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1439</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1924</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>6033</v>
       </c>
     </row>
     <row r="17">
@@ -5325,16 +5325,16 @@
         <v>5211</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2687</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1417</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1661</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>5765</v>
       </c>
     </row>
     <row r="18">
@@ -5356,16 +5356,16 @@
         <v>5688</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2262</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1068</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1646</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>4976</v>
       </c>
     </row>
     <row r="19">
@@ -5387,16 +5387,16 @@
         <v>5361</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2698</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1460</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1858</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>6016</v>
       </c>
     </row>
     <row r="20">
@@ -5418,16 +5418,16 @@
         <v>5798</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2876</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1578</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>5734</v>
       </c>
     </row>
     <row r="21">
@@ -5449,16 +5449,16 @@
         <v>6712</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>3048</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2140</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1937</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>7125</v>
       </c>
     </row>
     <row r="22">
@@ -5480,16 +5480,16 @@
         <v>5745</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>2858</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1959</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2356</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>7173</v>
       </c>
     </row>
     <row r="23">
@@ -5511,16 +5511,16 @@
         <v>6038</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1610</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1087</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1727</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>4424</v>
       </c>
     </row>
     <row r="24">
@@ -5542,16 +5542,16 @@
         <v>4664</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2195</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1654</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2115</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>5964</v>
       </c>
     </row>
     <row r="25">
@@ -5573,16 +5573,16 @@
         <v>4904</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>2612</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1684</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1893</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>6189</v>
       </c>
     </row>
     <row r="26">
@@ -5604,16 +5604,16 @@
         <v>5132</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>2880</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1593</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1674</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>6147</v>
       </c>
     </row>
     <row r="27">
@@ -5635,16 +5635,16 @@
         <v>5242</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>2451</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1452</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1381</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>5284</v>
       </c>
     </row>
     <row r="28">
@@ -5666,16 +5666,16 @@
         <v>6195</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>2677</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1713</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1536</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>5926</v>
       </c>
     </row>
     <row r="29">
@@ -5685,16 +5685,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>2387</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1611</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1761</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>5759</v>
       </c>
     </row>
     <row r="30">
@@ -5716,16 +5716,16 @@
         <v>6741</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2417</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1721</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1546</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>5684</v>
       </c>
     </row>
     <row r="31">
@@ -5747,16 +5747,16 @@
         <v>7259</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>2901</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2343</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2138</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>7382</v>
       </c>
     </row>
     <row r="32">
@@ -5778,16 +5778,16 @@
         <v>8124</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>2852</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1805</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1609</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>6266</v>
       </c>
     </row>
     <row r="33">
@@ -5809,16 +5809,16 @@
         <v>5040</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>2465</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>2167</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1874</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>6506</v>
       </c>
     </row>
     <row r="34">
@@ -5840,16 +5840,16 @@
         <v>6870</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>2487</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1954</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1781</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>6222</v>
       </c>
     </row>
     <row r="35">
@@ -5871,16 +5871,16 @@
         <v>5418</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>2079</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1659</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1633</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>5371</v>
       </c>
     </row>
     <row r="36">
@@ -5902,16 +5902,16 @@
         <v>2711</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>2615</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1686</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1494</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>5795</v>
       </c>
     </row>
     <row r="37">
@@ -5933,16 +5933,16 @@
         <v>5227</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>2167</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1334</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>4885</v>
       </c>
     </row>
     <row r="38">
@@ -5964,16 +5964,16 @@
         <v>5665</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>2191</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1488</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1441</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="39">
@@ -6502,7 +6502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6686,6 +6686,282 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>C:\TRC\trc_engine\outputs\weekly\Weekly W14-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W15-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W16-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W17-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W18-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W19-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W20-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>W21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W21-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>W22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W22-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>W23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W23-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>W24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W24-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>W25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W25-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>W26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W26-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>W27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W27-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>W28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W28-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>W29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W29-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>W30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W30-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>W31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W31-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>W32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W32-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>W33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W33-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>W34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W34-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>W35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W35-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>W36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W36-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>W37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W37-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -7982,73 +8258,73 @@
         <v>4073</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>0</v>
+        <v>2670</v>
       </c>
       <c r="R9" s="7" t="n">
-        <v>0</v>
+        <v>2687</v>
       </c>
       <c r="S9" s="7" t="n">
-        <v>0</v>
+        <v>2262</v>
       </c>
       <c r="T9" s="7" t="n">
-        <v>0</v>
+        <v>2698</v>
       </c>
       <c r="U9" s="7" t="n">
-        <v>0</v>
+        <v>2876</v>
       </c>
       <c r="V9" s="7" t="n">
-        <v>0</v>
+        <v>3048</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>0</v>
+        <v>2858</v>
       </c>
       <c r="X9" s="7" t="n">
-        <v>0</v>
+        <v>1610</v>
       </c>
       <c r="Y9" s="7" t="n">
-        <v>0</v>
+        <v>2195</v>
       </c>
       <c r="Z9" s="7" t="n">
-        <v>0</v>
+        <v>2612</v>
       </c>
       <c r="AA9" s="7" t="n">
-        <v>0</v>
+        <v>2880</v>
       </c>
       <c r="AB9" s="7" t="n">
-        <v>0</v>
+        <v>2451</v>
       </c>
       <c r="AC9" s="7" t="n">
-        <v>0</v>
+        <v>2677</v>
       </c>
       <c r="AD9" s="7" t="n">
-        <v>0</v>
+        <v>2387</v>
       </c>
       <c r="AE9" s="7" t="n">
-        <v>0</v>
+        <v>2417</v>
       </c>
       <c r="AF9" s="7" t="n">
-        <v>0</v>
+        <v>2901</v>
       </c>
       <c r="AG9" s="7" t="n">
-        <v>0</v>
+        <v>2852</v>
       </c>
       <c r="AH9" s="7" t="n">
-        <v>0</v>
+        <v>2465</v>
       </c>
       <c r="AI9" s="7" t="n">
-        <v>0</v>
+        <v>2487</v>
       </c>
       <c r="AJ9" s="7" t="n">
-        <v>0</v>
+        <v>2079</v>
       </c>
       <c r="AK9" s="7" t="n">
-        <v>0</v>
+        <v>2615</v>
       </c>
       <c r="AL9" s="7" t="n">
-        <v>0</v>
+        <v>2167</v>
       </c>
       <c r="AM9" s="7" t="n">
-        <v>0</v>
+        <v>2191</v>
       </c>
       <c r="AN9" s="7" t="n">
         <v>0</v>
@@ -8150,73 +8426,73 @@
         <v>1823</v>
       </c>
       <c r="Q10" s="7" t="n">
-        <v>0</v>
+        <v>1439</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>0</v>
+        <v>1417</v>
       </c>
       <c r="S10" s="7" t="n">
-        <v>0</v>
+        <v>1068</v>
       </c>
       <c r="T10" s="7" t="n">
-        <v>0</v>
+        <v>1460</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="V10" s="7" t="n">
-        <v>0</v>
+        <v>2140</v>
       </c>
       <c r="W10" s="7" t="n">
-        <v>0</v>
+        <v>1959</v>
       </c>
       <c r="X10" s="7" t="n">
-        <v>0</v>
+        <v>1087</v>
       </c>
       <c r="Y10" s="7" t="n">
-        <v>0</v>
+        <v>1654</v>
       </c>
       <c r="Z10" s="7" t="n">
-        <v>0</v>
+        <v>1684</v>
       </c>
       <c r="AA10" s="7" t="n">
-        <v>0</v>
+        <v>1593</v>
       </c>
       <c r="AB10" s="7" t="n">
-        <v>0</v>
+        <v>1452</v>
       </c>
       <c r="AC10" s="7" t="n">
-        <v>0</v>
+        <v>1713</v>
       </c>
       <c r="AD10" s="7" t="n">
-        <v>0</v>
+        <v>1611</v>
       </c>
       <c r="AE10" s="7" t="n">
-        <v>0</v>
+        <v>1721</v>
       </c>
       <c r="AF10" s="7" t="n">
-        <v>0</v>
+        <v>2343</v>
       </c>
       <c r="AG10" s="7" t="n">
-        <v>0</v>
+        <v>1805</v>
       </c>
       <c r="AH10" s="7" t="n">
-        <v>0</v>
+        <v>2167</v>
       </c>
       <c r="AI10" s="7" t="n">
-        <v>0</v>
+        <v>1954</v>
       </c>
       <c r="AJ10" s="7" t="n">
-        <v>0</v>
+        <v>1659</v>
       </c>
       <c r="AK10" s="7" t="n">
-        <v>0</v>
+        <v>1686</v>
       </c>
       <c r="AL10" s="7" t="n">
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AM10" s="7" t="n">
-        <v>0</v>
+        <v>1488</v>
       </c>
       <c r="AN10" s="7" t="n">
         <v>0</v>
@@ -8318,73 +8594,73 @@
         <v>3244</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>0</v>
+        <v>1924</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>0</v>
+        <v>1661</v>
       </c>
       <c r="S11" s="7" t="n">
-        <v>0</v>
+        <v>1646</v>
       </c>
       <c r="T11" s="7" t="n">
-        <v>0</v>
+        <v>1858</v>
       </c>
       <c r="U11" s="7" t="n">
-        <v>0</v>
+        <v>1578</v>
       </c>
       <c r="V11" s="7" t="n">
-        <v>0</v>
+        <v>1937</v>
       </c>
       <c r="W11" s="7" t="n">
-        <v>0</v>
+        <v>2356</v>
       </c>
       <c r="X11" s="7" t="n">
-        <v>0</v>
+        <v>1727</v>
       </c>
       <c r="Y11" s="7" t="n">
-        <v>0</v>
+        <v>2115</v>
       </c>
       <c r="Z11" s="7" t="n">
-        <v>0</v>
+        <v>1893</v>
       </c>
       <c r="AA11" s="7" t="n">
-        <v>0</v>
+        <v>1674</v>
       </c>
       <c r="AB11" s="7" t="n">
-        <v>0</v>
+        <v>1381</v>
       </c>
       <c r="AC11" s="7" t="n">
-        <v>0</v>
+        <v>1536</v>
       </c>
       <c r="AD11" s="7" t="n">
-        <v>0</v>
+        <v>1761</v>
       </c>
       <c r="AE11" s="7" t="n">
-        <v>0</v>
+        <v>1546</v>
       </c>
       <c r="AF11" s="7" t="n">
-        <v>0</v>
+        <v>2138</v>
       </c>
       <c r="AG11" s="7" t="n">
-        <v>0</v>
+        <v>1609</v>
       </c>
       <c r="AH11" s="7" t="n">
-        <v>0</v>
+        <v>1874</v>
       </c>
       <c r="AI11" s="7" t="n">
-        <v>0</v>
+        <v>1781</v>
       </c>
       <c r="AJ11" s="7" t="n">
-        <v>0</v>
+        <v>1633</v>
       </c>
       <c r="AK11" s="7" t="n">
-        <v>0</v>
+        <v>1494</v>
       </c>
       <c r="AL11" s="7" t="n">
-        <v>0</v>
+        <v>1334</v>
       </c>
       <c r="AM11" s="7" t="n">
-        <v>0</v>
+        <v>1441</v>
       </c>
       <c r="AN11" s="7" t="n">
         <v>0</v>
@@ -8818,73 +9094,73 @@
         <v>9294</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>0</v>
+        <v>5630</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>0</v>
+        <v>5485</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>0</v>
+        <v>5167</v>
       </c>
       <c r="T15" s="7" t="n">
-        <v>0</v>
+        <v>5660</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>0</v>
+        <v>5818</v>
       </c>
       <c r="V15" s="7" t="n">
-        <v>0</v>
+        <v>5621</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>0</v>
+        <v>5405</v>
       </c>
       <c r="X15" s="7" t="n">
-        <v>0</v>
+        <v>2868</v>
       </c>
       <c r="Y15" s="7" t="n">
-        <v>0</v>
+        <v>3882</v>
       </c>
       <c r="Z15" s="7" t="n">
-        <v>0</v>
+        <v>5064</v>
       </c>
       <c r="AA15" s="7" t="n">
-        <v>0</v>
+        <v>6432</v>
       </c>
       <c r="AB15" s="7" t="n">
-        <v>0</v>
+        <v>4591</v>
       </c>
       <c r="AC15" s="7" t="n">
-        <v>0</v>
+        <v>4739</v>
       </c>
       <c r="AD15" s="7" t="n">
-        <v>0</v>
+        <v>4684</v>
       </c>
       <c r="AE15" s="7" t="n">
-        <v>0</v>
+        <v>4029</v>
       </c>
       <c r="AF15" s="7" t="n">
-        <v>0</v>
+        <v>5245</v>
       </c>
       <c r="AG15" s="7" t="n">
-        <v>0</v>
+        <v>4473</v>
       </c>
       <c r="AH15" s="7" t="n">
-        <v>0</v>
+        <v>4463</v>
       </c>
       <c r="AI15" s="7" t="n">
-        <v>0</v>
+        <v>4175</v>
       </c>
       <c r="AJ15" s="7" t="n">
-        <v>0</v>
+        <v>3801</v>
       </c>
       <c r="AK15" s="7" t="n">
-        <v>0</v>
+        <v>4745</v>
       </c>
       <c r="AL15" s="7" t="n">
-        <v>0</v>
+        <v>4143</v>
       </c>
       <c r="AM15" s="7" t="n">
-        <v>0</v>
+        <v>3692</v>
       </c>
       <c r="AN15" s="7" t="n">
         <v>0</v>
@@ -8986,73 +9262,73 @@
         <v>4598</v>
       </c>
       <c r="Q16" s="7" t="n">
-        <v>0</v>
+        <v>3066</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>0</v>
+        <v>2748</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>0</v>
+        <v>2188</v>
       </c>
       <c r="T16" s="7" t="n">
-        <v>0</v>
+        <v>3119</v>
       </c>
       <c r="U16" s="7" t="n">
-        <v>0</v>
+        <v>2108</v>
       </c>
       <c r="V16" s="7" t="n">
-        <v>0</v>
+        <v>3306</v>
       </c>
       <c r="W16" s="7" t="n">
-        <v>0</v>
+        <v>3085</v>
       </c>
       <c r="X16" s="7" t="n">
-        <v>0</v>
+        <v>1981</v>
       </c>
       <c r="Y16" s="7" t="n">
-        <v>0</v>
+        <v>3272</v>
       </c>
       <c r="Z16" s="7" t="n">
-        <v>0</v>
+        <v>3214</v>
       </c>
       <c r="AA16" s="7" t="n">
-        <v>0</v>
+        <v>3418</v>
       </c>
       <c r="AB16" s="7" t="n">
-        <v>0</v>
+        <v>2942</v>
       </c>
       <c r="AC16" s="7" t="n">
-        <v>0</v>
+        <v>3589</v>
       </c>
       <c r="AD16" s="7" t="n">
-        <v>0</v>
+        <v>3318</v>
       </c>
       <c r="AE16" s="7" t="n">
-        <v>0</v>
+        <v>3425</v>
       </c>
       <c r="AF16" s="7" t="n">
-        <v>0</v>
+        <v>4756</v>
       </c>
       <c r="AG16" s="7" t="n">
-        <v>0</v>
+        <v>3297</v>
       </c>
       <c r="AH16" s="7" t="n">
-        <v>0</v>
+        <v>4209</v>
       </c>
       <c r="AI16" s="7" t="n">
-        <v>0</v>
+        <v>3295</v>
       </c>
       <c r="AJ16" s="7" t="n">
-        <v>0</v>
+        <v>3153</v>
       </c>
       <c r="AK16" s="7" t="n">
-        <v>0</v>
+        <v>3937</v>
       </c>
       <c r="AL16" s="7" t="n">
-        <v>0</v>
+        <v>2687</v>
       </c>
       <c r="AM16" s="7" t="n">
-        <v>0</v>
+        <v>2940</v>
       </c>
       <c r="AN16" s="7" t="n">
         <v>0</v>
@@ -9154,73 +9430,73 @@
         <v>7289</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>0</v>
+        <v>3101</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>0</v>
+        <v>3133</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>0</v>
+        <v>2977</v>
       </c>
       <c r="T17" s="7" t="n">
-        <v>0</v>
+        <v>2944</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>0</v>
+        <v>2493</v>
       </c>
       <c r="V17" s="7" t="n">
-        <v>0</v>
+        <v>2691</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>0</v>
+        <v>3205</v>
       </c>
       <c r="X17" s="7" t="n">
-        <v>0</v>
+        <v>2306</v>
       </c>
       <c r="Y17" s="7" t="n">
-        <v>0</v>
+        <v>3375</v>
       </c>
       <c r="Z17" s="7" t="n">
-        <v>0</v>
+        <v>3834</v>
       </c>
       <c r="AA17" s="7" t="n">
-        <v>0</v>
+        <v>2864</v>
       </c>
       <c r="AB17" s="7" t="n">
-        <v>0</v>
+        <v>2676</v>
       </c>
       <c r="AC17" s="7" t="n">
-        <v>0</v>
+        <v>2836</v>
       </c>
       <c r="AD17" s="7" t="n">
-        <v>0</v>
+        <v>3063</v>
       </c>
       <c r="AE17" s="7" t="n">
-        <v>0</v>
+        <v>2883</v>
       </c>
       <c r="AF17" s="7" t="n">
-        <v>0</v>
+        <v>3587</v>
       </c>
       <c r="AG17" s="7" t="n">
-        <v>0</v>
+        <v>2591</v>
       </c>
       <c r="AH17" s="7" t="n">
-        <v>0</v>
+        <v>3938</v>
       </c>
       <c r="AI17" s="7" t="n">
-        <v>0</v>
+        <v>3453</v>
       </c>
       <c r="AJ17" s="7" t="n">
-        <v>0</v>
+        <v>3238</v>
       </c>
       <c r="AK17" s="7" t="n">
-        <v>0</v>
+        <v>2887</v>
       </c>
       <c r="AL17" s="7" t="n">
-        <v>0</v>
+        <v>2826</v>
       </c>
       <c r="AM17" s="7" t="n">
-        <v>0</v>
+        <v>2986</v>
       </c>
       <c r="AN17" s="7" t="n">
         <v>0</v>

--- a/files/power_outage_area/Power_Cuts_2026_Area_Summary.xlsx
+++ b/files/power_outage_area/Power_Cuts_2026_Area_Summary.xlsx
@@ -643,22 +643,22 @@
         </is>
       </c>
       <c r="C2" s="9" t="n">
-        <v>96529</v>
+        <v>99091</v>
       </c>
       <c r="D2" s="9" t="n">
-        <v>44.40095122882389</v>
+        <v>44.40655179367675</v>
       </c>
       <c r="E2" s="9" t="inlineStr"/>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>180652:00:00</t>
+          <t>185274:00:00</t>
         </is>
       </c>
       <c r="G2" s="9" t="n">
-        <v>180652</v>
+        <v>185274</v>
       </c>
       <c r="H2" s="9" t="n">
-        <v>44.79267654665057</v>
+        <v>44.65940317215446</v>
       </c>
     </row>
     <row r="3">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>55483</v>
+        <v>56955</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>25.52080698058444</v>
+        <v>25.52376257590356</v>
       </c>
       <c r="E3" s="10" t="inlineStr"/>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>103907:00:00</t>
+          <t>107363:00:00</t>
         </is>
       </c>
       <c r="G3" s="10" t="n">
-        <v>103907</v>
+        <v>107363</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>25.7637482116601</v>
+        <v>25.87933278696428</v>
       </c>
     </row>
     <row r="4">
@@ -703,22 +703,22 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>65391</v>
+        <v>67099</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>30.07824179059167</v>
+        <v>30.06968563041968</v>
       </c>
       <c r="E4" s="11" t="inlineStr"/>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>118748:00:00</t>
+          <t>122223:00:00</t>
         </is>
       </c>
       <c r="G4" s="11" t="n">
-        <v>118748</v>
+        <v>122223</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>29.44357524168933</v>
+        <v>29.46126404088126</v>
       </c>
     </row>
   </sheetData>
@@ -1175,7 +1175,7 @@
         <v>2191</v>
       </c>
       <c r="AM2" s="9" t="n">
-        <v>0</v>
+        <v>2562</v>
       </c>
       <c r="AN2" s="9" t="n">
         <v>0</v>
@@ -1338,7 +1338,7 @@
         <v>1488</v>
       </c>
       <c r="AM3" s="10" t="n">
-        <v>0</v>
+        <v>1472</v>
       </c>
       <c r="AN3" s="10" t="n">
         <v>0</v>
@@ -1501,7 +1501,7 @@
         <v>1441</v>
       </c>
       <c r="AM4" s="11" t="n">
-        <v>0</v>
+        <v>1708</v>
       </c>
       <c r="AN4" s="11" t="n">
         <v>0</v>
@@ -1664,7 +1664,7 @@
         <v>5120</v>
       </c>
       <c r="AM5" s="12" t="n">
-        <v>0</v>
+        <v>5742</v>
       </c>
       <c r="AN5" s="12" t="n">
         <v>0</v>
@@ -2163,7 +2163,7 @@
         <v>3692</v>
       </c>
       <c r="AM2" s="9" t="n">
-        <v>0</v>
+        <v>4622</v>
       </c>
       <c r="AN2" s="9" t="n">
         <v>0</v>
@@ -2326,7 +2326,7 @@
         <v>2940</v>
       </c>
       <c r="AM3" s="10" t="n">
-        <v>0</v>
+        <v>3456</v>
       </c>
       <c r="AN3" s="10" t="n">
         <v>0</v>
@@ -2489,7 +2489,7 @@
         <v>2986</v>
       </c>
       <c r="AM4" s="11" t="n">
-        <v>0</v>
+        <v>3475</v>
       </c>
       <c r="AN4" s="11" t="n">
         <v>0</v>
@@ -2652,7 +2652,7 @@
         <v>9618</v>
       </c>
       <c r="AM5" s="12" t="n">
-        <v>0</v>
+        <v>11553</v>
       </c>
       <c r="AN5" s="12" t="n">
         <v>0</v>
@@ -3455,16 +3455,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>2562</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>1472</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>1708</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>5742</v>
       </c>
     </row>
     <row r="40">
@@ -4491,16 +4491,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>4622</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>3456</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>3475</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>11553</v>
       </c>
     </row>
     <row r="40">
@@ -5995,16 +5995,16 @@
         <v>5554</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>2562</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1472</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1708</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>5742</v>
       </c>
     </row>
     <row r="40">
@@ -6502,7 +6502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6962,6 +6962,18 @@
       <c r="B38" t="inlineStr">
         <is>
           <t>C:\TRC\trc_engine\outputs\weekly\Weekly W37-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>W38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W38-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8339,7 @@
         <v>2191</v>
       </c>
       <c r="AN9" s="7" t="n">
-        <v>0</v>
+        <v>2562</v>
       </c>
       <c r="AO9" s="7" t="n">
         <v>0</v>
@@ -8495,7 +8507,7 @@
         <v>1488</v>
       </c>
       <c r="AN10" s="7" t="n">
-        <v>0</v>
+        <v>1472</v>
       </c>
       <c r="AO10" s="7" t="n">
         <v>0</v>
@@ -8663,7 +8675,7 @@
         <v>1441</v>
       </c>
       <c r="AN11" s="7" t="n">
-        <v>0</v>
+        <v>1708</v>
       </c>
       <c r="AO11" s="7" t="n">
         <v>0</v>
@@ -9163,7 +9175,7 @@
         <v>3692</v>
       </c>
       <c r="AN15" s="7" t="n">
-        <v>0</v>
+        <v>4622</v>
       </c>
       <c r="AO15" s="7" t="n">
         <v>0</v>
@@ -9331,7 +9343,7 @@
         <v>2940</v>
       </c>
       <c r="AN16" s="7" t="n">
-        <v>0</v>
+        <v>3456</v>
       </c>
       <c r="AO16" s="7" t="n">
         <v>0</v>
@@ -9499,7 +9511,7 @@
         <v>2986</v>
       </c>
       <c r="AN17" s="7" t="n">
-        <v>0</v>
+        <v>3475</v>
       </c>
       <c r="AO17" s="7" t="n">
         <v>0</v>

--- a/files/power_outage_area/Power_Cuts_2026_Area_Summary.xlsx
+++ b/files/power_outage_area/Power_Cuts_2026_Area_Summary.xlsx
@@ -643,22 +643,22 @@
         </is>
       </c>
       <c r="C2" s="9" t="n">
-        <v>99091</v>
+        <v>101379</v>
       </c>
       <c r="D2" s="9" t="n">
-        <v>44.40655179367675</v>
+        <v>44.40293277737872</v>
       </c>
       <c r="E2" s="9" t="inlineStr"/>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>185274:00:00</t>
+          <t>189238:00:00</t>
         </is>
       </c>
       <c r="G2" s="9" t="n">
-        <v>185274</v>
+        <v>189238</v>
       </c>
       <c r="H2" s="9" t="n">
-        <v>44.65940317215446</v>
+        <v>44.58197478278897</v>
       </c>
     </row>
     <row r="3">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>56955</v>
+        <v>58397</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>25.52376257590356</v>
+        <v>25.57727009933601</v>
       </c>
       <c r="E3" s="10" t="inlineStr"/>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>107363:00:00</t>
+          <t>109949:00:00</t>
         </is>
       </c>
       <c r="G3" s="10" t="n">
-        <v>107363</v>
+        <v>109949</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>25.87933278696428</v>
+        <v>25.9025330292693</v>
       </c>
     </row>
     <row r="4">
@@ -703,22 +703,22 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>67099</v>
+        <v>68540</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>30.06968563041968</v>
+        <v>30.01979712328527</v>
       </c>
       <c r="E4" s="11" t="inlineStr"/>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>122223:00:00</t>
+          <t>125285:00:00</t>
         </is>
       </c>
       <c r="G4" s="11" t="n">
-        <v>122223</v>
+        <v>125285</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>29.46126404088126</v>
+        <v>29.51549218794173</v>
       </c>
     </row>
   </sheetData>
@@ -1178,7 +1178,7 @@
         <v>2562</v>
       </c>
       <c r="AN2" s="9" t="n">
-        <v>0</v>
+        <v>2288</v>
       </c>
       <c r="AO2" s="9" t="n">
         <v>0</v>
@@ -1341,7 +1341,7 @@
         <v>1472</v>
       </c>
       <c r="AN3" s="10" t="n">
-        <v>0</v>
+        <v>1442</v>
       </c>
       <c r="AO3" s="10" t="n">
         <v>0</v>
@@ -1504,7 +1504,7 @@
         <v>1708</v>
       </c>
       <c r="AN4" s="11" t="n">
-        <v>0</v>
+        <v>1441</v>
       </c>
       <c r="AO4" s="11" t="n">
         <v>0</v>
@@ -1667,7 +1667,7 @@
         <v>5742</v>
       </c>
       <c r="AN5" s="12" t="n">
-        <v>0</v>
+        <v>5171</v>
       </c>
       <c r="AO5" s="12" t="n">
         <v>0</v>
@@ -2166,7 +2166,7 @@
         <v>4622</v>
       </c>
       <c r="AN2" s="9" t="n">
-        <v>0</v>
+        <v>3964</v>
       </c>
       <c r="AO2" s="9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
         <v>3456</v>
       </c>
       <c r="AN3" s="10" t="n">
-        <v>0</v>
+        <v>2586</v>
       </c>
       <c r="AO3" s="10" t="n">
         <v>0</v>
@@ -2492,7 +2492,7 @@
         <v>3475</v>
       </c>
       <c r="AN4" s="11" t="n">
-        <v>0</v>
+        <v>3062</v>
       </c>
       <c r="AO4" s="11" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>11553</v>
       </c>
       <c r="AN5" s="12" t="n">
-        <v>0</v>
+        <v>9612</v>
       </c>
       <c r="AO5" s="12" t="n">
         <v>0</v>
@@ -3474,16 +3474,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>2288</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>1442</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>1441</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>5171</v>
       </c>
     </row>
     <row r="41">
@@ -4510,16 +4510,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>3964</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>2586</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>3062</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>9612</v>
       </c>
     </row>
     <row r="41">
@@ -6026,16 +6026,16 @@
         <v>5132</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>2288</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1442</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1441</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>5171</v>
       </c>
     </row>
     <row r="41">
@@ -6502,7 +6502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6974,6 +6974,18 @@
       <c r="B39" t="inlineStr">
         <is>
           <t>C:\TRC\trc_engine\outputs\weekly\Weekly W38-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>W39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W39-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8354,7 @@
         <v>2562</v>
       </c>
       <c r="AO9" s="7" t="n">
-        <v>0</v>
+        <v>2288</v>
       </c>
       <c r="AP9" s="7" t="n">
         <v>0</v>
@@ -8510,7 +8522,7 @@
         <v>1472</v>
       </c>
       <c r="AO10" s="7" t="n">
-        <v>0</v>
+        <v>1442</v>
       </c>
       <c r="AP10" s="7" t="n">
         <v>0</v>
@@ -8678,7 +8690,7 @@
         <v>1708</v>
       </c>
       <c r="AO11" s="7" t="n">
-        <v>0</v>
+        <v>1441</v>
       </c>
       <c r="AP11" s="7" t="n">
         <v>0</v>
@@ -9178,7 +9190,7 @@
         <v>4622</v>
       </c>
       <c r="AO15" s="7" t="n">
-        <v>0</v>
+        <v>3964</v>
       </c>
       <c r="AP15" s="7" t="n">
         <v>0</v>
@@ -9346,7 +9358,7 @@
         <v>3456</v>
       </c>
       <c r="AO16" s="7" t="n">
-        <v>0</v>
+        <v>2586</v>
       </c>
       <c r="AP16" s="7" t="n">
         <v>0</v>
@@ -9514,7 +9526,7 @@
         <v>3475</v>
       </c>
       <c r="AO17" s="7" t="n">
-        <v>0</v>
+        <v>3062</v>
       </c>
       <c r="AP17" s="7" t="n">
         <v>0</v>

--- a/files/power_outage_area/Power_Cuts_2026_Area_Summary.xlsx
+++ b/files/power_outage_area/Power_Cuts_2026_Area_Summary.xlsx
@@ -643,22 +643,22 @@
         </is>
       </c>
       <c r="C2" s="9" t="n">
-        <v>101379</v>
+        <v>103302</v>
       </c>
       <c r="D2" s="9" t="n">
-        <v>44.40293277737872</v>
+        <v>44.31850358230726</v>
       </c>
       <c r="E2" s="9" t="inlineStr"/>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>189238:00:00</t>
+          <t>192826:00:00</t>
         </is>
       </c>
       <c r="G2" s="9" t="n">
-        <v>189238</v>
+        <v>192826</v>
       </c>
       <c r="H2" s="9" t="n">
-        <v>44.58197478278897</v>
+        <v>44.45904693393834</v>
       </c>
     </row>
     <row r="3">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>58397</v>
+        <v>59718</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>25.57727009933601</v>
+        <v>25.6201467244412</v>
       </c>
       <c r="E3" s="10" t="inlineStr"/>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>109949:00:00</t>
+          <t>112595:00:00</t>
         </is>
       </c>
       <c r="G3" s="10" t="n">
-        <v>109949</v>
+        <v>112595</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>25.9025330292693</v>
+        <v>25.96053638786672</v>
       </c>
     </row>
     <row r="4">
@@ -703,22 +703,22 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>68540</v>
+        <v>70070</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>30.01979712328527</v>
+        <v>30.06134969325153</v>
       </c>
       <c r="E4" s="11" t="inlineStr"/>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>125285:00:00</t>
+          <t>128295:00:00</t>
         </is>
       </c>
       <c r="G4" s="11" t="n">
-        <v>125285</v>
+        <v>128295</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>29.51549218794173</v>
+        <v>29.58041667819495</v>
       </c>
     </row>
   </sheetData>
@@ -1181,7 +1181,7 @@
         <v>2288</v>
       </c>
       <c r="AO2" s="9" t="n">
-        <v>0</v>
+        <v>1923</v>
       </c>
       <c r="AP2" s="9" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
         <v>1442</v>
       </c>
       <c r="AO3" s="10" t="n">
-        <v>0</v>
+        <v>1321</v>
       </c>
       <c r="AP3" s="10" t="n">
         <v>0</v>
@@ -1507,7 +1507,7 @@
         <v>1441</v>
       </c>
       <c r="AO4" s="11" t="n">
-        <v>0</v>
+        <v>1530</v>
       </c>
       <c r="AP4" s="11" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>5171</v>
       </c>
       <c r="AO5" s="12" t="n">
-        <v>0</v>
+        <v>4774</v>
       </c>
       <c r="AP5" s="12" t="n">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>3964</v>
       </c>
       <c r="AO2" s="9" t="n">
-        <v>0</v>
+        <v>3588</v>
       </c>
       <c r="AP2" s="9" t="n">
         <v>0</v>
@@ -2332,7 +2332,7 @@
         <v>2586</v>
       </c>
       <c r="AO3" s="10" t="n">
-        <v>0</v>
+        <v>2646</v>
       </c>
       <c r="AP3" s="10" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>3062</v>
       </c>
       <c r="AO4" s="11" t="n">
-        <v>0</v>
+        <v>3010</v>
       </c>
       <c r="AP4" s="11" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>9612</v>
       </c>
       <c r="AO5" s="12" t="n">
-        <v>0</v>
+        <v>9244</v>
       </c>
       <c r="AP5" s="12" t="n">
         <v>0</v>
@@ -3493,16 +3493,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>1923</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>1321</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1530</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>4774</v>
       </c>
     </row>
     <row r="42">
@@ -4529,16 +4529,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>3588</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>2646</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>3010</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>9244</v>
       </c>
     </row>
     <row r="42">
@@ -6057,16 +6057,16 @@
         <v>5673</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1923</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1321</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1530</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>4774</v>
       </c>
     </row>
     <row r="42">
@@ -6502,7 +6502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6986,6 +6986,18 @@
       <c r="B40" t="inlineStr">
         <is>
           <t>C:\TRC\trc_engine\outputs\weekly\Weekly W39-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>W40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>C:\TRC\trc_engine\outputs\weekly\Weekly W40-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -8357,7 +8369,7 @@
         <v>2288</v>
       </c>
       <c r="AP9" s="7" t="n">
-        <v>0</v>
+        <v>1923</v>
       </c>
       <c r="AQ9" s="7" t="n">
         <v>0</v>
@@ -8525,7 +8537,7 @@
         <v>1442</v>
       </c>
       <c r="AP10" s="7" t="n">
-        <v>0</v>
+        <v>1321</v>
       </c>
       <c r="AQ10" s="7" t="n">
         <v>0</v>
@@ -8693,7 +8705,7 @@
         <v>1441</v>
       </c>
       <c r="AP11" s="7" t="n">
-        <v>0</v>
+        <v>1530</v>
       </c>
       <c r="AQ11" s="7" t="n">
         <v>0</v>
@@ -9193,7 +9205,7 @@
         <v>3964</v>
       </c>
       <c r="AP15" s="7" t="n">
-        <v>0</v>
+        <v>3588</v>
       </c>
       <c r="AQ15" s="7" t="n">
         <v>0</v>
@@ -9361,7 +9373,7 @@
         <v>2586</v>
       </c>
       <c r="AP16" s="7" t="n">
-        <v>0</v>
+        <v>2646</v>
       </c>
       <c r="AQ16" s="7" t="n">
         <v>0</v>
@@ -9529,7 +9541,7 @@
         <v>3062</v>
       </c>
       <c r="AP17" s="7" t="n">
-        <v>0</v>
+        <v>3010</v>
       </c>
       <c r="AQ17" s="7" t="n">
         <v>0</v>
